--- a/SGC-CKN/Excel/50ebec0b-e37e-4a84-a2de-c7dee01c7689_Cọc_khoan_nhồi_331_D1200_08-04-2026.xlsx
+++ b/SGC-CKN/Excel/50ebec0b-e37e-4a84-a2de-c7dee01c7689_Cọc_khoan_nhồi_331_D1200_08-04-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>331</t>
+    <t>P331</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/50ebec0b-e37e-4a84-a2de-c7dee01c7689_Cọc_khoan_nhồi_331_D1200_08-04-2026.xlsx
+++ b/SGC-CKN/Excel/50ebec0b-e37e-4a84-a2de-c7dee01c7689_Cọc_khoan_nhồi_331_D1200_08-04-2026.xlsx
@@ -1606,7 +1606,7 @@
         <v>59</v>
       </c>
       <c r="F21" s="16">
-        <v>61.4</v>
+        <v>-61.4</v>
       </c>
       <c r="G21" s="16">
         <v>-64.4</v>
@@ -1615,10 +1615,10 @@
         <v>1.38</v>
       </c>
       <c r="I21" s="16">
-        <v>125.8</v>
-      </c>
-      <c r="J21" s="8">
-        <v>90.94</v>
+        <v>3</v>
+      </c>
+      <c r="J21" s="12">
+        <v>2.17</v>
       </c>
       <c r="K21" s="17" t="s">
         <v>29</v>
@@ -1679,16 +1679,16 @@
         <v>-65.3</v>
       </c>
       <c r="G23" s="5">
-        <v>73.4</v>
+        <v>-73.4</v>
       </c>
       <c r="H23" s="5">
         <v>2.08</v>
       </c>
       <c r="I23" s="5">
-        <v>138.7</v>
-      </c>
-      <c r="J23" s="8">
-        <v>66.58</v>
+        <v>8.1</v>
+      </c>
+      <c r="J23" s="12">
+        <v>3.89</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>29</v>
@@ -1711,10 +1711,10 @@
         <v>67</v>
       </c>
       <c r="F24" s="9">
-        <v>73.4</v>
+        <v>-73.4</v>
       </c>
       <c r="G24" s="9">
-        <v>77.17</v>
+        <v>-77.17</v>
       </c>
       <c r="H24" s="9">
         <v>1.63</v>
@@ -2168,7 +2168,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="16">
-        <v>61.4</v>
+        <v>-61.4</v>
       </c>
       <c r="F12" s="16">
         <v>-64.4</v>
@@ -2177,10 +2177,10 @@
         <v>1.38</v>
       </c>
       <c r="H12" s="16">
-        <v>125.8</v>
-      </c>
-      <c r="I12" s="8">
-        <v>90.94</v>
+        <v>3</v>
+      </c>
+      <c r="I12" s="12">
+        <v>2.17</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2229,16 +2229,16 @@
         <v>-65.3</v>
       </c>
       <c r="F14" s="5">
-        <v>73.4</v>
+        <v>-73.4</v>
       </c>
       <c r="G14" s="5">
         <v>2.08</v>
       </c>
       <c r="H14" s="5">
-        <v>138.7</v>
-      </c>
-      <c r="I14" s="8">
-        <v>66.58</v>
+        <v>8.1</v>
+      </c>
+      <c r="I14" s="12">
+        <v>3.89</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2255,10 +2255,10 @@
         <v>1</v>
       </c>
       <c r="E15" s="9">
-        <v>73.4</v>
+        <v>-73.4</v>
       </c>
       <c r="F15" s="9">
-        <v>77.17</v>
+        <v>-77.17</v>
       </c>
       <c r="G15" s="9">
         <v>1.63</v>
@@ -2287,16 +2287,16 @@
         <v>0</v>
       </c>
       <c r="F16" s="42">
-        <v>77.17</v>
+        <v>-77.17</v>
       </c>
       <c r="G16" s="42">
         <v>16.38</v>
       </c>
       <c r="H16" s="42">
-        <v>330.57</v>
+        <v>77.17</v>
       </c>
       <c r="I16" s="42">
-        <v>20.18</v>
+        <v>4.71</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/50ebec0b-e37e-4a84-a2de-c7dee01c7689_Cọc_khoan_nhồi_331_D1200_08-04-2026.xlsx
+++ b/SGC-CKN/Excel/50ebec0b-e37e-4a84-a2de-c7dee01c7689_Cọc_khoan_nhồi_331_D1200_08-04-2026.xlsx
@@ -1679,16 +1679,16 @@
         <v>-65.3</v>
       </c>
       <c r="G23" s="5">
-        <v>-73.4</v>
+        <v>73.4</v>
       </c>
       <c r="H23" s="5">
         <v>2.08</v>
       </c>
       <c r="I23" s="5">
-        <v>8.1</v>
-      </c>
-      <c r="J23" s="12">
-        <v>3.89</v>
+        <v>138.7</v>
+      </c>
+      <c r="J23" s="8">
+        <v>66.58</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>29</v>
@@ -1711,10 +1711,10 @@
         <v>67</v>
       </c>
       <c r="F24" s="9">
-        <v>-73.4</v>
+        <v>73.4</v>
       </c>
       <c r="G24" s="9">
-        <v>-77.17</v>
+        <v>77.17</v>
       </c>
       <c r="H24" s="9">
         <v>1.63</v>
@@ -2229,16 +2229,16 @@
         <v>-65.3</v>
       </c>
       <c r="F14" s="5">
-        <v>-73.4</v>
+        <v>73.4</v>
       </c>
       <c r="G14" s="5">
         <v>2.08</v>
       </c>
       <c r="H14" s="5">
-        <v>8.1</v>
-      </c>
-      <c r="I14" s="12">
-        <v>3.89</v>
+        <v>138.7</v>
+      </c>
+      <c r="I14" s="8">
+        <v>66.58</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2255,10 +2255,10 @@
         <v>1</v>
       </c>
       <c r="E15" s="9">
-        <v>-73.4</v>
+        <v>73.4</v>
       </c>
       <c r="F15" s="9">
-        <v>-77.17</v>
+        <v>77.17</v>
       </c>
       <c r="G15" s="9">
         <v>1.63</v>
@@ -2287,16 +2287,16 @@
         <v>0</v>
       </c>
       <c r="F16" s="42">
-        <v>-77.17</v>
+        <v>77.17</v>
       </c>
       <c r="G16" s="42">
         <v>16.38</v>
       </c>
       <c r="H16" s="42">
-        <v>77.17</v>
+        <v>207.77</v>
       </c>
       <c r="I16" s="42">
-        <v>4.71</v>
+        <v>12.68</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/50ebec0b-e37e-4a84-a2de-c7dee01c7689_Cọc_khoan_nhồi_331_D1200_08-04-2026.xlsx
+++ b/SGC-CKN/Excel/50ebec0b-e37e-4a84-a2de-c7dee01c7689_Cọc_khoan_nhồi_331_D1200_08-04-2026.xlsx
@@ -1679,16 +1679,16 @@
         <v>-65.3</v>
       </c>
       <c r="G23" s="5">
-        <v>73.4</v>
+        <v>-73.4</v>
       </c>
       <c r="H23" s="5">
         <v>2.08</v>
       </c>
       <c r="I23" s="5">
-        <v>138.7</v>
-      </c>
-      <c r="J23" s="8">
-        <v>66.58</v>
+        <v>8.1</v>
+      </c>
+      <c r="J23" s="12">
+        <v>3.89</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>29</v>
@@ -1711,10 +1711,10 @@
         <v>67</v>
       </c>
       <c r="F24" s="9">
-        <v>73.4</v>
+        <v>-73.4</v>
       </c>
       <c r="G24" s="9">
-        <v>77.17</v>
+        <v>-77.17</v>
       </c>
       <c r="H24" s="9">
         <v>1.63</v>
@@ -2229,16 +2229,16 @@
         <v>-65.3</v>
       </c>
       <c r="F14" s="5">
-        <v>73.4</v>
+        <v>-73.4</v>
       </c>
       <c r="G14" s="5">
         <v>2.08</v>
       </c>
       <c r="H14" s="5">
-        <v>138.7</v>
-      </c>
-      <c r="I14" s="8">
-        <v>66.58</v>
+        <v>8.1</v>
+      </c>
+      <c r="I14" s="12">
+        <v>3.89</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2255,10 +2255,10 @@
         <v>1</v>
       </c>
       <c r="E15" s="9">
-        <v>73.4</v>
+        <v>-73.4</v>
       </c>
       <c r="F15" s="9">
-        <v>77.17</v>
+        <v>-77.17</v>
       </c>
       <c r="G15" s="9">
         <v>1.63</v>
@@ -2287,16 +2287,16 @@
         <v>0</v>
       </c>
       <c r="F16" s="42">
-        <v>77.17</v>
+        <v>-77.17</v>
       </c>
       <c r="G16" s="42">
         <v>16.38</v>
       </c>
       <c r="H16" s="42">
-        <v>207.77</v>
+        <v>77.17</v>
       </c>
       <c r="I16" s="42">
-        <v>12.68</v>
+        <v>4.71</v>
       </c>
     </row>
   </sheetData>
